--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.748985122066513</v>
+        <v>1.584210082335808</v>
       </c>
       <c r="D2" t="n">
-        <v>11.71793575191954</v>
+        <v>1.904164559686925</v>
       </c>
       <c r="E2" t="n">
-        <v>3.388184063422208</v>
+        <v>0.5505799103061088</v>
       </c>
       <c r="F2" t="n">
-        <v>4.244385336178403</v>
+        <v>0.6897126171289906</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2.972616995222097</v>
+        <v>0.4830502617235908</v>
       </c>
       <c r="D3" t="n">
-        <v>3.229165079562733</v>
+        <v>0.5247393254289442</v>
       </c>
       <c r="E3" t="n">
-        <v>3.388184063422208</v>
+        <v>0.5505799103061088</v>
       </c>
       <c r="F3" t="n">
-        <v>4.244385336178403</v>
+        <v>0.6897126171289906</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
